--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_43.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_43.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2788524.710881341</v>
+        <v>2781657.717932684</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162900552</v>
+        <v>286.4107162900655</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162900552</v>
+        <v>286.4107162900655</v>
       </c>
     </row>
     <row r="11">
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -985,13 +985,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1030,10 +1030,10 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>346.530169394292</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1219,16 +1219,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>308.4311513056531</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>140.1718664988258</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>385</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>99.47457824299391</v>
+        <v>103.4399696284084</v>
       </c>
       <c r="D11" t="n">
         <v>60.33915573984979</v>
@@ -1380,7 +1380,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>547.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1507,13 +1507,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>145.0509054352709</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X12" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1617,7 +1617,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H14" t="n">
         <v>58.00965870352741</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="R15" t="n">
         <v>197.2737972923793</v>
@@ -1735,7 +1735,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U15" t="n">
         <v>50.21035976018675</v>
@@ -1747,10 +1747,10 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1854,7 +1854,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
         <v>58.00965870352741</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T17" t="n">
         <v>236.6755817285639</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>104.5622219498565</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1963,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>197.2737972923793</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
@@ -2094,7 +2094,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2158,10 +2158,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>62.67776252544254</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>436.872294727342</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
@@ -2328,10 +2328,10 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>62.67776252544254</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>239.5984974349628</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>197.2737972923793</v>
@@ -2598,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2632,13 +2632,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>73.77767497096178</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>64.74007562773993</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>49.39139276613435</v>
@@ -2799,13 +2799,13 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G29" t="n">
         <v>53.75737228701621</v>
       </c>
       <c r="H29" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2881,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S30" t="n">
         <v>116.5639999646113</v>
@@ -3042,10 +3042,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3106,7 +3106,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>98.0381390959345</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3118,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>80.50967533902136</v>
       </c>
       <c r="R33" t="n">
         <v>197.2737972923793</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3343,10 +3343,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>98.0381390959345</v>
       </c>
       <c r="D36" t="n">
-        <v>239.5984974349628</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>197.2737972923793</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3555,7 +3555,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U38" t="n">
-        <v>299.2212965486107</v>
+        <v>303.1866879340253</v>
       </c>
       <c r="V38" t="n">
         <v>279.8510241668239</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>547.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3643,7 +3643,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>49.39139276613435</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T41" t="n">
         <v>236.6755817285639</v>
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T42" t="n">
-        <v>118.0355277429562</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U42" t="n">
         <v>50.21035976018675</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T44" t="n">
         <v>236.6755817285639</v>
@@ -4054,7 +4054,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>91.60958778454074</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178217</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
@@ -4333,13 +4333,13 @@
         <v>793.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4485,22 +4485,22 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
@@ -4561,16 +4561,16 @@
         <v>30.8</v>
       </c>
       <c r="K5" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="L5" t="n">
-        <v>30.8</v>
+        <v>396.55</v>
       </c>
       <c r="M5" t="n">
-        <v>396.55</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>777.6999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="O5" t="n">
         <v>1158.85</v>
@@ -4582,28 +4582,28 @@
         <v>1540</v>
       </c>
       <c r="R5" t="n">
-        <v>1511.00384708544</v>
+        <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="C6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="D6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="E6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="F6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="G6" t="n">
-        <v>585.6429020987573</v>
+        <v>30.8</v>
       </c>
       <c r="H6" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S6" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T6" t="n">
-        <v>964.8227613033797</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U6" t="n">
-        <v>964.6102766971304</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V6" t="n">
-        <v>949.9530371097363</v>
+        <v>439.752262066048</v>
       </c>
       <c r="W6" t="n">
-        <v>917.2528927563742</v>
+        <v>50.86337317715914</v>
       </c>
       <c r="X6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>404.9974293695179</v>
+        <v>404.0685093339813</v>
       </c>
       <c r="C7" t="n">
-        <v>530.9994351879537</v>
+        <v>530.0705151524171</v>
       </c>
       <c r="D7" t="n">
-        <v>644.3185793129538</v>
+        <v>643.3896592774172</v>
       </c>
       <c r="E7" t="n">
-        <v>762.1474835243669</v>
+        <v>761.2185634888302</v>
       </c>
       <c r="F7" t="n">
-        <v>886.5084561163023</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="G7" t="n">
-        <v>1039.915022003188</v>
+        <v>1038.986101967651</v>
       </c>
       <c r="H7" t="n">
-        <v>1209.431607162585</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I7" t="n">
-        <v>1430.564486098668</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4758,10 +4758,10 @@
         <v>30.8</v>
       </c>
       <c r="X7" t="n">
-        <v>181.8307910241935</v>
+        <v>180.9018709886569</v>
       </c>
       <c r="Y7" t="n">
-        <v>293.2400917032258</v>
+        <v>292.3111716676892</v>
       </c>
     </row>
     <row r="8">
@@ -4795,25 +4795,25 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.9500000000033</v>
+        <v>411.9500000000029</v>
       </c>
       <c r="K8" t="n">
-        <v>777.6999999999905</v>
+        <v>777.699999999993</v>
       </c>
       <c r="L8" t="n">
-        <v>777.6999999999905</v>
+        <v>777.699999999993</v>
       </c>
       <c r="M8" t="n">
-        <v>1158.849999999995</v>
+        <v>1158.849999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>1540</v>
+        <v>1158.849999999997</v>
       </c>
       <c r="O8" t="n">
-        <v>1540</v>
+        <v>1158.849999999997</v>
       </c>
       <c r="P8" t="n">
-        <v>1540</v>
+        <v>1158.849999999997</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="C9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="D9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="E9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="F9" t="n">
-        <v>585.6429020987573</v>
+        <v>30.8</v>
       </c>
       <c r="G9" t="n">
-        <v>585.6429020987573</v>
+        <v>30.8</v>
       </c>
       <c r="H9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I9" t="n">
         <v>30.8</v>
@@ -4907,19 +4907,19 @@
         <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>964.6102766971304</v>
+        <v>823.2350173651719</v>
       </c>
       <c r="V9" t="n">
-        <v>949.9530371097363</v>
+        <v>808.5777777777778</v>
       </c>
       <c r="W9" t="n">
-        <v>917.2528927563742</v>
+        <v>419.6888888888889</v>
       </c>
       <c r="X9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>897.189519579215</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1074.126545134783</v>
+        <v>614.1386027233684</v>
       </c>
       <c r="C10" t="n">
-        <v>1074.126545134783</v>
+        <v>740.1406085418042</v>
       </c>
       <c r="D10" t="n">
-        <v>1187.445689259783</v>
+        <v>853.4597526668043</v>
       </c>
       <c r="E10" t="n">
-        <v>1305.274593471196</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="F10" t="n">
-        <v>1429.635566063132</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="G10" t="n">
-        <v>1429.635566063132</v>
+        <v>1038.986101967651</v>
       </c>
       <c r="H10" t="n">
-        <v>1429.635566063132</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I10" t="n">
         <v>1429.635566063132</v>
@@ -4983,22 +4983,22 @@
         <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>256.125934252978</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>502.6771268912646</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="V10" t="n">
-        <v>701.4985197772105</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="W10" t="n">
-        <v>873.3894380368879</v>
+        <v>239.9411733538506</v>
       </c>
       <c r="X10" t="n">
-        <v>1024.420229061081</v>
+        <v>390.971964378044</v>
       </c>
       <c r="Y10" t="n">
-        <v>1074.126545134783</v>
+        <v>502.3812650570763</v>
       </c>
     </row>
     <row r="11">
@@ -5011,16 +5011,16 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
         <v>103.3156148520479</v>
@@ -5044,13 +5044,13 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O11" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5135,25 +5135,25 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>647.3506049216877</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S12" t="n">
-        <v>529.6091908160197</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T12" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U12" t="n">
-        <v>422.9747211415747</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V12" t="n">
-        <v>357.8124310491301</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W12" t="n">
-        <v>211.2963649528968</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X12" t="n">
-        <v>140.7279412706871</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y12" t="n">
         <v>90.8376455473191</v>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
         <v>103.3156148520479</v>
@@ -5269,25 +5269,25 @@
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="K14" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="L14" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M14" t="n">
-        <v>946.8779417665908</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N14" t="n">
-        <v>1500.287941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P14" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q14" t="n">
         <v>2236</v>
@@ -5296,25 +5296,25 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5369,28 +5369,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1200.152420368536</v>
+        <v>1136.841549130715</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135527</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
         <v>90.8376455473191</v>
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F17" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G17" t="n">
         <v>103.3156148520479</v>
@@ -5506,22 +5506,22 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="L17" t="n">
-        <v>690.5809049473327</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M17" t="n">
         <v>690.5809049473327</v>
       </c>
       <c r="N17" t="n">
-        <v>690.5809049473327</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O17" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>1797.400904947332</v>
@@ -5533,25 +5533,25 @@
         <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T17" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V17" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X17" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y17" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="18">
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>402.0654643105373</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C18" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
         <v>44.72</v>
@@ -5606,31 +5606,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T18" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V18" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W18" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X18" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
         <v>44.72</v>
@@ -5743,52 +5743,52 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="L20" t="n">
-        <v>989.4391130376558</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M20" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N20" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D21" t="n">
         <v>44.72</v>
@@ -5843,31 +5843,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>584.0397336838671</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5931,10 +5931,10 @@
         <v>44.72</v>
       </c>
       <c r="T22" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U22" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V22" t="n">
         <v>521.9574820108303</v>
@@ -5971,7 +5971,7 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5998,7 +5998,7 @@
         <v>1500.287941766591</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>297.950717050992</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C24" t="n">
-        <v>286.7386842777402</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D24" t="n">
-        <v>286.7386842777402</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E24" t="n">
-        <v>286.7386842777402</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F24" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="G24" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="H24" t="n">
         <v>44.72</v>
@@ -6080,31 +6080,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U24" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V24" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W24" t="n">
-        <v>453.3150492306369</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>382.7466255484273</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y24" t="n">
-        <v>332.8563298250593</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="25">
@@ -6226,22 +6226,22 @@
         <v>989.4391130376558</v>
       </c>
       <c r="M26" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N26" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O26" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P26" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
       </c>
       <c r="R26" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S26" t="n">
         <v>2085.68327354774</v>
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C27" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D27" t="n">
-        <v>44.72</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="E27" t="n">
         <v>44.72</v>
@@ -6338,10 +6338,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X27" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y27" t="n">
-        <v>154.1485167851398</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="28">
@@ -6442,10 +6442,10 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F29" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H29" t="n">
         <v>44.72</v>
@@ -6454,22 +6454,22 @@
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="L29" t="n">
-        <v>989.4391130376558</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M29" t="n">
-        <v>1500.287941766591</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N29" t="n">
-        <v>2053.697941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="O29" t="n">
-        <v>2236</v>
+        <v>1682.59</v>
       </c>
       <c r="P29" t="n">
         <v>2236</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>409.4673863086053</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6557,28 +6557,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>494.2632948060406</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>444.3729990826726</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6642,22 +6642,22 @@
         <v>44.72</v>
       </c>
       <c r="T31" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U31" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X31" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y31" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="32">
@@ -6685,31 +6685,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K32" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="L32" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="M32" t="n">
-        <v>1500.287941766591</v>
+        <v>555.568828728935</v>
       </c>
       <c r="N32" t="n">
-        <v>2053.697941766591</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O32" t="n">
-        <v>2236</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="P32" t="n">
-        <v>2236</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>472.7782575464261</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C33" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D33" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E33" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F33" t="n">
-        <v>373.7498342171993</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H33" t="n">
         <v>44.72</v>
@@ -6791,31 +6791,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1200.152420368536</v>
+        <v>1118.829515985686</v>
       </c>
       <c r="R33" t="n">
-        <v>1000.885958457041</v>
+        <v>919.5630540741914</v>
       </c>
       <c r="S33" t="n">
-        <v>883.1445443513733</v>
+        <v>801.8216399685234</v>
       </c>
       <c r="T33" t="n">
-        <v>827.2276097882281</v>
+        <v>745.9047054053782</v>
       </c>
       <c r="U33" t="n">
-        <v>776.5100746769283</v>
+        <v>695.1871702940784</v>
       </c>
       <c r="V33" t="n">
-        <v>711.3477845844836</v>
+        <v>630.0248802016338</v>
       </c>
       <c r="W33" t="n">
-        <v>628.142589726071</v>
+        <v>546.8196853432211</v>
       </c>
       <c r="X33" t="n">
-        <v>557.5741660438614</v>
+        <v>476.2512616610114</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.6838703204934</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="34">
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
@@ -6931,49 +6931,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L35" t="n">
-        <v>1542.849113037656</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M35" t="n">
-        <v>1542.849113037656</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N35" t="n">
-        <v>2096.259113037656</v>
+        <v>1129.18</v>
       </c>
       <c r="O35" t="n">
-        <v>2096.259113037656</v>
+        <v>1682.59</v>
       </c>
       <c r="P35" t="n">
-        <v>2096.259113037656</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,19 +6983,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>297.950717050992</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>286.7386842777402</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G36" t="n">
         <v>44.72</v>
@@ -7028,31 +7028,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>453.3150492306369</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>382.7466255484273</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y36" t="n">
-        <v>332.8563298250593</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="37">
@@ -7171,7 +7171,7 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>989.4391130376558</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M38" t="n">
         <v>1129.18</v>
@@ -7189,13 +7189,13 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
         <v>1544.373295489988</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>647.3506049216877</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S39" t="n">
-        <v>529.6091908160197</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T39" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U39" t="n">
-        <v>422.9747211415747</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V39" t="n">
-        <v>357.8124310491301</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W39" t="n">
-        <v>274.6072361907174</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X39" t="n">
-        <v>140.7279412706871</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="40">
@@ -7378,43 +7378,43 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>179.7320762183977</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>179.7320762183977</v>
+        <v>598.13</v>
       </c>
       <c r="L41" t="n">
-        <v>179.7320762183977</v>
+        <v>1151.54</v>
       </c>
       <c r="M41" t="n">
-        <v>690.5809049473327</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N41" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
         <v>1797.400904947332</v>
@@ -7429,25 +7429,25 @@
         <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7505,10 +7505,10 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>529.6091908160197</v>
+        <v>819.8336731135527</v>
       </c>
       <c r="T42" t="n">
         <v>410.3813850150538</v>
@@ -7536,10 +7536,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
         <v>1010.366979583462</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7642,22 +7642,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>989.4391130376558</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N44" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="O44" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="P44" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192207</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="46">
@@ -7976,7 +7976,7 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>846.6934025142796</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>70.24786957409245</v>
@@ -7985,7 +7985,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,19 +8204,19 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>913.7065720867618</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450937</v>
+        <v>420.0430062450932</v>
       </c>
       <c r="K8" t="n">
-        <v>369.4444444444315</v>
+        <v>369.4444444444345</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423222</v>
+        <v>929.2621276423215</v>
       </c>
       <c r="N8" t="n">
-        <v>862.24895806984</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274883</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8687,7 +8687,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>777.3630622928068</v>
       </c>
       <c r="O11" t="n">
         <v>629.2478695740924</v>
@@ -8696,7 +8696,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>356.9661774925453</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,7 +8912,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121691</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -8927,13 +8927,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>370.3619737970638</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>128.4277587171436</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>356.9661774925453</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9641,10 +9641,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>300.4011642636528</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9869,7 +9869,7 @@
         <v>559</v>
       </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>801.385149773304</v>
       </c>
       <c r="N26" t="n">
         <v>1036.248958069835</v>
@@ -9878,10 +9878,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>184.4305532057413</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,13 +10097,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,10 +10112,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>254.3913627391524</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q29" t="n">
         <v>172.8226843274854</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>254.3913627391524</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>193.2279078336117</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>685.4145387153926</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>313.9750954005603</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10814,10 +10814,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="M38" t="n">
-        <v>685.4145387153925</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
@@ -11045,22 +11045,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>171.4188408091284</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>613.624792633873</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11285,7 +11285,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>559</v>
@@ -11294,7 +11294,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
@@ -11303,7 +11303,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>356.9661774925453</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -26275,7 +26275,7 @@
         <v>1353789.266154872</v>
       </c>
       <c r="D2" t="n">
-        <v>1353789.266154872</v>
+        <v>1353789.266154871</v>
       </c>
       <c r="E2" t="n">
         <v>1353830.31835754</v>
@@ -26302,7 +26302,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="M2" t="n">
-        <v>1353830.318357541</v>
+        <v>1353830.31835754</v>
       </c>
       <c r="N2" t="n">
         <v>1353830.31835754</v>
@@ -26311,7 +26311,7 @@
         <v>1353830.31835754</v>
       </c>
       <c r="P2" t="n">
-        <v>1353830.318357541</v>
+        <v>1353830.31835754</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984991</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>590319.5412553629</v>
+        <v>588803.6855670469</v>
       </c>
       <c r="C6" t="n">
-        <v>727897.5213891767</v>
+        <v>726381.6657008611</v>
       </c>
       <c r="D6" t="n">
-        <v>729958.2933014928</v>
+        <v>728442.4376131765</v>
       </c>
       <c r="E6" t="n">
-        <v>406076.9151310049</v>
+        <v>404335.0653178975</v>
       </c>
       <c r="F6" t="n">
-        <v>749267.810476509</v>
+        <v>747525.9606634013</v>
       </c>
       <c r="G6" t="n">
-        <v>751213.3869446943</v>
+        <v>749471.5371315868</v>
       </c>
       <c r="H6" t="n">
-        <v>753161.6637619961</v>
+        <v>751419.813948888</v>
       </c>
       <c r="I6" t="n">
-        <v>755112.6604053563</v>
+        <v>753370.8105922487</v>
       </c>
       <c r="J6" t="n">
-        <v>341546.3966069814</v>
+        <v>339804.5467938735</v>
       </c>
       <c r="K6" t="n">
-        <v>759022.8923592006</v>
+        <v>757281.042546093</v>
       </c>
       <c r="L6" t="n">
-        <v>760982.16791946</v>
+        <v>759240.3181063526</v>
       </c>
       <c r="M6" t="n">
-        <v>701696.2438154399</v>
+        <v>699954.3940023319</v>
       </c>
       <c r="N6" t="n">
-        <v>764909.1408502929</v>
+        <v>763167.2910371851</v>
       </c>
       <c r="O6" t="n">
-        <v>486876.8801080306</v>
+        <v>485135.0302949232</v>
       </c>
       <c r="P6" t="n">
-        <v>768847.4829590415</v>
+        <v>767105.6331459336</v>
       </c>
     </row>
   </sheetData>
@@ -27002,7 +27002,7 @@
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -27036,7 +27036,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -27060,7 +27060,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -27088,7 +27088,7 @@
         <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27764,13 +27764,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>17.3083845693742</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27809,10 +27809,10 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>67.98049779722811</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>145.809871968566</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>399.0616969338014</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27998,16 +27998,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>31.20509103222372</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28043,16 +28043,16 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>260.038493261361</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>34.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,28 +28065,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
       </c>
       <c r="E10" t="n">
+        <v>313.4251305076246</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
         <v>400</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>400</v>
       </c>
-      <c r="G10" t="n">
-        <v>245.04387284153</v>
-      </c>
-      <c r="H10" t="n">
-        <v>228.7711261016186</v>
-      </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28119,13 +28119,13 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>337.6737529239084</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28147,7 +28147,7 @@
         <v>350</v>
       </c>
       <c r="C11" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="D11" t="n">
         <v>350</v>
@@ -28159,7 +28159,7 @@
         <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
@@ -28271,7 +28271,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28286,13 +28286,13 @@
         <v>350</v>
       </c>
       <c r="W12" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="X12" t="n">
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28396,7 +28396,7 @@
         <v>350</v>
       </c>
       <c r="G14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H14" t="n">
         <v>350</v>
@@ -28432,7 +28432,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>173.0792650904796</v>
+        <v>110.4015025650371</v>
       </c>
       <c r="R15" t="n">
         <v>350</v>
@@ -28514,7 +28514,7 @@
         <v>350</v>
       </c>
       <c r="T15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>350</v>
@@ -28526,10 +28526,10 @@
         <v>350</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y15" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16">
@@ -28633,7 +28633,7 @@
         <v>350</v>
       </c>
       <c r="G17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H17" t="n">
         <v>350</v>
@@ -28669,7 +28669,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T17" t="n">
         <v>350</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
@@ -28706,7 +28706,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -28742,10 +28742,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>350</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
@@ -28873,7 +28873,7 @@
         <v>350</v>
       </c>
       <c r="H20" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28937,10 +28937,10 @@
         <v>350</v>
       </c>
       <c r="C21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -28979,10 +28979,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>110.4015025650372</v>
+        <v>350</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
@@ -29067,13 +29067,13 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
+        <v>350</v>
+      </c>
+      <c r="U22" t="n">
+        <v>350</v>
+      </c>
+      <c r="V22" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U22" t="n">
-        <v>350</v>
-      </c>
-      <c r="V22" t="n">
-        <v>350</v>
       </c>
       <c r="W22" t="n">
         <v>350</v>
@@ -29107,10 +29107,10 @@
         <v>350</v>
       </c>
       <c r="G23" t="n">
+        <v>350</v>
+      </c>
+      <c r="H23" t="n">
         <v>346.0346086145855</v>
-      </c>
-      <c r="H23" t="n">
-        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29183,13 +29183,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>92.56958975145832</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>350</v>
@@ -29377,10 +29377,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29411,13 +29411,13 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
@@ -29474,7 +29474,7 @@
         <v>350</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y27" t="n">
         <v>350</v>
@@ -29578,13 +29578,13 @@
         <v>350</v>
       </c>
       <c r="F29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G29" t="n">
         <v>350</v>
       </c>
       <c r="H29" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I29" t="n">
         <v>150.0811596826846</v>
@@ -29648,7 +29648,7 @@
         <v>350</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
@@ -29660,10 +29660,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29693,7 +29693,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S30" t="n">
         <v>350</v>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C31" t="n">
         <v>350</v>
@@ -29778,7 +29778,7 @@
         <v>350</v>
       </c>
       <c r="T31" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U31" t="n">
         <v>350</v>
@@ -29821,10 +29821,10 @@
         <v>350</v>
       </c>
       <c r="H32" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29885,7 +29885,7 @@
         <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>263.0617733495848</v>
+        <v>350</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -29897,10 +29897,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>217.1263858913485</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>92.56958975145824</v>
       </c>
       <c r="R33" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30122,10 +30122,10 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="D36" t="n">
-        <v>108.3391894627398</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30134,7 +30134,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
         <v>350</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30334,7 +30334,7 @@
         <v>350</v>
       </c>
       <c r="U38" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="V38" t="n">
         <v>350</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30422,7 +30422,7 @@
         <v>350</v>
       </c>
       <c r="X39" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="Y39" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30565,7 +30565,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T41" t="n">
         <v>350</v>
@@ -30641,13 +30641,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T42" t="n">
-        <v>287.3222374745576</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>350</v>
@@ -30678,7 +30678,7 @@
         <v>350</v>
       </c>
       <c r="D43" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30802,7 +30802,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T44" t="n">
         <v>350</v>
@@ -30833,7 +30833,7 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30878,10 +30878,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
@@ -34755,7 +34755,7 @@
         <v>385</v>
       </c>
       <c r="N2" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34983,19 +34983,19 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>369.4444444444444</v>
+        <v>385</v>
       </c>
       <c r="N5" t="n">
         <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35138,10 +35138,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>110.5409231326582</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>151.6180515036939</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385.0000000000034</v>
+        <v>385.0000000000029</v>
       </c>
       <c r="K8" t="n">
-        <v>369.4444444444315</v>
+        <v>369.4444444444345</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>385.0000000000049</v>
+        <v>385.0000000000042</v>
       </c>
       <c r="N8" t="n">
-        <v>385.0000000000048</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>385.000000000003</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,28 +35351,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>32.44422567066807</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35405,13 +35405,13 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>50.20840007444606</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35466,7 +35466,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>300.1141042229716</v>
       </c>
       <c r="O11" t="n">
         <v>559</v>
@@ -35475,7 +35475,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>184.1434931650599</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,7 +35691,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612659</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -35706,13 +35706,13 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q14" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>136.375834564038</v>
+      </c>
+      <c r="M17" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N17" t="n">
         <v>559</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -36186,7 +36186,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>184.1434931650599</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,13 +36353,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V22" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W22" t="n">
         <v>123.6271901612903</v>
@@ -36420,10 +36420,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36648,7 +36648,7 @@
         <v>559</v>
       </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>257.1230221309867</v>
       </c>
       <c r="N26" t="n">
         <v>559</v>
@@ -36657,10 +36657,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,13 +36876,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="L29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,10 +36891,10 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -37010,7 +37010,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C31" t="n">
         <v>77.27475335195533</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U31" t="n">
         <v>199.0416087255421</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37128,13 +37128,13 @@
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q35" t="n">
-        <v>141.1524110730749</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37593,10 +37593,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="M38" t="n">
-        <v>141.1524110730752</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
@@ -37824,22 +37824,22 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37964,7 +37964,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E43" t="n">
         <v>69.01909516304346</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38064,7 +38064,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>559</v>
@@ -38073,7 +38073,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -38082,7 +38082,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
